--- a/public/uploads/files/SampleFormat.xlsx
+++ b/public/uploads/files/SampleFormat.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8010"/>
+    <workbookView windowWidth="19200" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,28 +27,133 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>Item No.</t>
   </si>
   <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>StockQty</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Subcategory</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Star</t>
+  </si>
+  <si>
+    <t>Movement</t>
+  </si>
+  <si>
+    <t>MRP PRICE</t>
+  </si>
+  <si>
+    <t>Special Price</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Key Features</t>
+  </si>
+  <si>
+    <t>image1</t>
+  </si>
+  <si>
+    <t>image2</t>
+  </si>
+  <si>
+    <t>image3</t>
+  </si>
+  <si>
+    <t>overview images</t>
+  </si>
+  <si>
+    <t>overview_description</t>
+  </si>
+  <si>
+    <t>variants</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
+    <t>Extend Warranty</t>
+  </si>
+  <si>
     <t>VGACTTTROLLEY</t>
   </si>
   <si>
+    <t>TT TROLLEY FOR UPS BATTERY V-GUARD ACCESSORIES</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Fabrics Cover &amp; Stand</t>
+  </si>
+  <si>
+    <t>V-Guard</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Trolley Display ( Battery Space ) Dimension : LENGTH - 55 , HEIGHT - 50 , WIDTH - 30.Trolley Weight - 5.3 kg , Loading Capacity - 70 kg.Screw - less easy installation.Suitable for all type single inverter - batteries ( flat and tall tubular batteries both ).Prevents battery acid water spillage.5 Wheels, 2 Sides Part,1 Base Part,1 Top Part, 1 Front Cover.( No Back Cover )Top can be removed for filling water in the battery.</t>
+  </si>
+  <si>
+    <t>HUpizgrlAGIIbGDC.jpg</t>
+  </si>
+  <si>
+    <t>iC7MPdTJcQ5XPD5U.jpg</t>
+  </si>
+  <si>
+    <t>HSGrqhSBymfLIdqa.jpg</t>
+  </si>
+  <si>
     <t>Active</t>
   </si>
   <si>
+    <t>[{"year":2,"amount":1500},{"year":3,"amount":2000}]</t>
+  </si>
+  <si>
     <t>VGACCWINDZYTROL</t>
+  </si>
+  <si>
+    <t>WINDZY T-N TROLLY AIRCOOLER V-GUARD ACCESSORIES</t>
+  </si>
+  <si>
+    <t>Sturdy and durable construction : The air cooler trolley is a high-quality, sturdy and durable product designed to provide a secure and stable base for your air cooler.Non-adjustable design for added stability and security : Its non-adjustable design ensures that your air cooler stays in place, preventing any wobbling or tipping over.4 castor wheels for easy mobility and maneuverability : The 4 castor wheels 360 degree movable make it easy to move the trolley and the air cooler around, allowing you to position it wherever you need it.Sleek and modern design that is both functional and stylish : The trolley has a sleek and modern design that will complement any decor and is sure to impress your guests.Powder-coated finish that resists rust and ensures long-lasting durability :Its powder-coated finish not only adds to its stylish appearance but also provides rust resistance, ensuring long-lasting durability.This air cooler trolley is perfect for use in small to medium-sized rooms, apartments, and offices, providing you with cool air wherever you need it.100-liter capacity for handling even the largest air coolers : With a 100-liter capacity, this trolley can easily handle even the largest air coolers, making it a practical and convenient accessory. and when assembled size Length of 55 cm, width of 55 cm, and height of 48 cm.</t>
+  </si>
+  <si>
+    <t>KY1ixc23rwkD0bPb.jpg</t>
+  </si>
+  <si>
+    <t>g9J8PEMl50b6oJgh.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -56,16 +161,353 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -73,17 +515,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -409,43 +1140,200 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="14.375" defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2">
+        <v>1499</v>
+      </c>
+      <c r="K2">
+        <v>1499</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>1190</v>
+      </c>
+      <c r="K3">
+        <v>412</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A2:A3 A1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:T3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>